--- a/naver-place-crawler/results_health/부평_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부평_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 부평점</t>
+          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>miraclebym02@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1334-5596</t>
+          <t>0507-1412-0034</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
+          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/all.night_official</t>
+          <t>https://www.instagram.com/miracle.gym02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41wqc</t>
+          <t>https://talk.naver.com/ct/webpfty</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1306</v>
+        <v>1893</v>
       </c>
       <c r="Q2" t="n">
-        <v>1177</v>
+        <v>949</v>
       </c>
       <c r="R2" t="n">
-        <v>2483</v>
+        <v>2842</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1342318850</t>
+          <t>35823978</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342318850</t>
+          <t>https://m.place.naver.com/place/35823978</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>머슬프로짐 PT 헬스</t>
+          <t>올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rkdals5404@naver.com</t>
+          <t>all_night_b@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1445-7902</t>
+          <t>0507-1334-5596</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
+          <t>인천 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/all.night_official</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41wqc</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1707</v>
+        <v>1308</v>
       </c>
       <c r="Q3" t="n">
-        <v>1511</v>
+        <v>920</v>
       </c>
       <c r="R3" t="n">
-        <v>3218</v>
+        <v>2228</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>142646646</t>
+          <t>1342318850</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/142646646</t>
+          <t>https://m.place.naver.com/place/1342318850</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
+          <t>스포애니 부평역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>spoany86@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1412-0034</t>
+          <t>0507-1339-9618</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
+          <t>인천 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany86</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/webpfty</t>
+          <t>https://talk.naver.com/ct/w4aher</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1882</v>
+        <v>1315</v>
       </c>
       <c r="Q4" t="n">
-        <v>960</v>
+        <v>3049</v>
       </c>
       <c r="R4" t="n">
-        <v>2842</v>
+        <v>4364</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>35823978</t>
+          <t>1118966019</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35823978</t>
+          <t>https://m.place.naver.com/place/1118966019</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -854,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>오빠네헬스장&amp;PT 부평점</t>
+          <t>머슬프로짐 PT 헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>oppagym@naver.com</t>
+          <t>rkdals5404@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1361-1167</t>
+          <t>0507-1445-7902</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 부평구 부흥로 265 501호</t>
+          <t>인천 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rkdals5404</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,24 +890,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vmvq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>768</v>
+        <v>1707</v>
       </c>
       <c r="Q5" t="n">
-        <v>2420</v>
+        <v>1506</v>
       </c>
       <c r="R5" t="n">
-        <v>3188</v>
+        <v>3213</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1538103381</t>
+          <t>142646646</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538103381</t>
+          <t>https://m.place.naver.com/place/142646646</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -952,44 +952,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 부평역점</t>
+          <t>짐박스피트니스 부평시장역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany86@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1339-9618</t>
+          <t>0507-1471-0163</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
+          <t>인천 부평구 부흥로 277 1~4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://gymboxx.com/onceinayear?gym=72</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4aher</t>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1306</v>
+        <v>2045</v>
       </c>
       <c r="Q6" t="n">
-        <v>3019</v>
+        <v>74</v>
       </c>
       <c r="R6" t="n">
-        <v>4325</v>
+        <v>2119</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1118966019</t>
+          <t>1569809175</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1118966019</t>
+          <t>https://m.place.naver.com/place/1569809175</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피트니스 연구소 부평동암역점</t>
+          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lfitness4@naver.com</t>
+          <t>ironfitnesssamsan@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1396-2222</t>
+          <t>0507-1483-2126</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 부평구 경원대로 1041 4층 피트니스 연구소 부평동암역점</t>
+          <t>인천 부평구 부평북로 448 로얄프라자 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.fitnessinstitute.co.kr</t>
+          <t>https://blog.naver.com/ironfitnesssamsan</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4arsy</t>
+          <t>https://talk.naver.com/ct/w451o2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2644</v>
+        <v>707</v>
       </c>
       <c r="Q7" t="n">
-        <v>856</v>
+        <v>291</v>
       </c>
       <c r="R7" t="n">
-        <v>3500</v>
+        <v>998</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1038730081</t>
+          <t>1098353648</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1038730081</t>
+          <t>https://m.place.naver.com/place/1098353648</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1169</v>
+        <v>1176</v>
       </c>
       <c r="Q8" t="n">
-        <v>915</v>
+        <v>925</v>
       </c>
       <c r="R8" t="n">
-        <v>2084</v>
+        <v>2101</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1277,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1298,7 +1302,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="Q9" t="n">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="R9" t="n">
-        <v>1466</v>
+        <v>1475</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1332,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>874</v>
+        <v>893</v>
       </c>
       <c r="Q10" t="n">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="R10" t="n">
-        <v>1324</v>
+        <v>1351</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1430,42 +1434,46 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>온정필라테스&amp;PT 산곡점</t>
+          <t>레디짐 부평점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ktg191800@naver.com</t>
+          <t>readygym2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1319-4573</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 부평구 마장로 320 2층 207호, 산곡역 2번출구에서 도보 2분 한화프라자 2층</t>
+          <t>인천 부평구 원적로 434 혜성프라자 B1 레디짐 부평점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.readygym.co.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1485,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4lmji</t>
+          <t>https://talk.naver.com/ct/wf5j2sx</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,17 +1503,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>328</v>
+        <v>911</v>
       </c>
       <c r="Q11" t="n">
-        <v>609</v>
+        <v>2241</v>
       </c>
       <c r="R11" t="n">
-        <v>937</v>
+        <v>3152</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1522,111 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1452652224</t>
+          <t>1207888173</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1452652224</t>
+          <t>https://m.place.naver.com/place/1207888173</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>필라테스 린 산곡점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pilateslean_sangok@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1311-1654</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천 부평구 원적로 412 5층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2024471908</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024471908</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부평_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부평_헬스장.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1893</v>
+        <v>1899</v>
       </c>
       <c r="Q2" t="n">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="R2" t="n">
-        <v>2842</v>
+        <v>2852</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 부평점</t>
+          <t>스포애니 부평역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>spoany86@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1334-5596</t>
+          <t>0507-1339-9618</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
+          <t>인천 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/all.night_official</t>
+          <t>https://blog.naver.com/spoany86</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41wqc</t>
+          <t>https://talk.naver.com/ct/w4aher</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1308</v>
+        <v>1315</v>
       </c>
       <c r="Q3" t="n">
-        <v>920</v>
+        <v>3057</v>
       </c>
       <c r="R3" t="n">
-        <v>2228</v>
+        <v>4372</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1342318850</t>
+          <t>1118966019</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342318850</t>
+          <t>https://m.place.naver.com/place/1118966019</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포애니 부평역점</t>
+          <t>올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spoany86@naver.com</t>
+          <t>all_night_b@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1339-9618</t>
+          <t>0507-1334-5596</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
+          <t>인천 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany86</t>
+          <t>https://www.instagram.com/all.night_official</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4aher</t>
+          <t>https://talk.naver.com/ct/w41wqc</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="Q4" t="n">
-        <v>3049</v>
+        <v>920</v>
       </c>
       <c r="R4" t="n">
-        <v>4364</v>
+        <v>2230</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1118966019</t>
+          <t>1342318850</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1118966019</t>
+          <t>https://m.place.naver.com/place/1342318850</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>머슬프로짐 PT 헬스</t>
+          <t>스포애니 부평시장역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rkdals5404@naver.com</t>
+          <t>spoany_70@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1445-7902</t>
+          <t>0507-1428-9618</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
+          <t>인천 부평구 부평대로 83 강남타워 9, 10층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rkdals5404</t>
+          <t>https://blog.naver.com/spoany_70</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -900,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w441cj</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1707</v>
+        <v>1526</v>
       </c>
       <c r="Q5" t="n">
-        <v>1506</v>
+        <v>2033</v>
       </c>
       <c r="R5" t="n">
-        <v>3213</v>
+        <v>3559</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>142646646</t>
+          <t>1163734622</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/142646646</t>
+          <t>https://m.place.naver.com/place/1163734622</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -952,38 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐박스피트니스 부평시장역점</t>
+          <t>머슬프로짐 PT 헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>rkdals5404@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1471-0163</t>
+          <t>0507-1445-7902</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 부평구 부흥로 277 1~4층</t>
+          <t>인천 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=72</t>
+          <t>https://blog.naver.com/rkdals5404</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -998,17 +998,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2045</v>
+        <v>1707</v>
       </c>
       <c r="Q6" t="n">
-        <v>74</v>
+        <v>1506</v>
       </c>
       <c r="R6" t="n">
-        <v>2119</v>
+        <v>3213</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1569809175</t>
+          <t>142646646</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1569809175</t>
+          <t>https://m.place.naver.com/place/142646646</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
+          <t>피트니스 연구소 부평산곡점 헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ironfitnesssamsan@naver.com</t>
+          <t>lfitness5@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1483-2126</t>
+          <t>0507-1349-2251</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 부평구 부평북로 448 로얄프라자 2층</t>
+          <t>인천 부평구 원적로 295 더 루츠 스퀘어 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ironfitnesssamsan</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w451o2</t>
+          <t>https://talk.naver.com/ct/w40cxc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>707</v>
+        <v>986</v>
       </c>
       <c r="Q7" t="n">
-        <v>291</v>
+        <v>491</v>
       </c>
       <c r="R7" t="n">
-        <v>998</v>
+        <v>1477</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1098353648</t>
+          <t>1338376061</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098353648</t>
+          <t>https://m.place.naver.com/place/1338376061</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>휘트니스피플우먼 부평점</t>
+          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>msgym_01@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1330-3912</t>
+          <t>032-330-3334</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 부평구 부평대로 19-1 도시프라자빌딩 7층 701호</t>
+          <t>인천 부평구 체육관로 34 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/msgym_01/223768835115</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44qaq</t>
+          <t>https://talk.naver.com/ct/wcbsfx</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1176</v>
+        <v>895</v>
       </c>
       <c r="Q8" t="n">
-        <v>925</v>
+        <v>458</v>
       </c>
       <c r="R8" t="n">
-        <v>2101</v>
+        <v>1353</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1619023009</t>
+          <t>1350569862</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619023009</t>
+          <t>https://m.place.naver.com/place/1350569862</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피트니스 연구소 부평산곡점 헬스PT</t>
+          <t>카우짐 백운역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lfitness5@naver.com</t>
+          <t>cowgym_24@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1349-2251</t>
+          <t>0507-1370-4255</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천 부평구 마장로 75 대경빌딩 B1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,12 +1293,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40cxc</t>
+          <t>https://talk.naver.com/ct/w413n5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>986</v>
+        <v>801</v>
       </c>
       <c r="Q9" t="n">
-        <v>489</v>
+        <v>433</v>
       </c>
       <c r="R9" t="n">
-        <v>1475</v>
+        <v>1234</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1338376061</t>
+          <t>1852598877</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338376061</t>
+          <t>https://m.place.naver.com/place/1852598877</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
+          <t>무무바디짐 부평점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>msgym_01@naver.com</t>
+          <t>qudan79@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-330-3334</t>
+          <t>0507-1440-0638</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 부평구 체육관로 34 7층</t>
+          <t>인천 부평구 경원대로 1358 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/msgym_01/223768835115</t>
+          <t>https://blog.naver.com/qudan79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcbsfx</t>
+          <t>https://talk.naver.com/ct/wzebqsn</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>893</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>458</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1351</v>
+        <v>28</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,66 +1420,66 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1350569862</t>
+          <t>2061355439</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350569862</t>
+          <t>https://m.place.naver.com/place/2061355439</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>레디짐 부평점 헬스 PT</t>
+          <t>3세트짐 체형교정센터 부평본점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>readygym2@naver.com</t>
+          <t>lineup_pt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1319-4573</t>
+          <t>0507-1323-8788</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 부평구 원적로 434 혜성프라자 B1 레디짐 부평점 헬스&amp;PT</t>
+          <t>인천 부평구 경원대로 1404 1003호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.readygym.co.kr</t>
+          <t>https://blog.naver.com/lineup_pt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wf5j2sx</t>
+          <t>https://talk.naver.com/ct/w4eq6k9</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>911</v>
+        <v>369</v>
       </c>
       <c r="Q11" t="n">
-        <v>2241</v>
+        <v>456</v>
       </c>
       <c r="R11" t="n">
-        <v>3152</v>
+        <v>825</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,17 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1207888173</t>
+          <t>1774897291</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1207888173</t>
+          <t>https://m.place.naver.com/place/1774897291</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1604,10 +1600,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1626,7 +1622,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부평_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부평_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1437,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3세트짐 체형교정센터 부평본점</t>
+          <t>필라테스 린 산곡점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lineup_pt@naver.com</t>
+          <t>pilateslean_sangok@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1323-8788</t>
+          <t>0507-1311-1654</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 부평구 경원대로 1404 1003호</t>
+          <t>인천 부평구 원적로 412 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lineup_pt</t>
+          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1484,14 +1484,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4eq6k9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1499,17 +1495,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>456</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>825</v>
+        <v>2</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,109 +1514,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1774897291</t>
+          <t>2024471908</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774897291</t>
+          <t>https://m.place.naver.com/place/2024471908</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>필라테스 린 산곡점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>pilateslean_sangok@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1311-1654</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>인천 부평구 원적로 412 5층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2024471908</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2024471908</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/부평_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부평_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>그린짐</t>
+          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>green_gym@naver.com</t>
+          <t>miraclebym02@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1482-4423</t>
+          <t>0507-1412-0034</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 부평구 부평북로 339 2층</t>
+          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/green_gym</t>
+          <t>https://www.instagram.com/miracle.gym02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fs9p</t>
+          <t>https://talk.naver.com/ct/webpfty</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>321</v>
+        <v>1899</v>
       </c>
       <c r="Q2" t="n">
-        <v>822</v>
+        <v>955</v>
       </c>
       <c r="R2" t="n">
-        <v>1143</v>
+        <v>2854</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1527477204</t>
+          <t>35823978</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1527477204</t>
+          <t>https://m.place.naver.com/place/35823978</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
+          <t>스포애니 부평시장역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>miraclebym02@naver.com</t>
+          <t>spoany_70@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1412-0034</t>
+          <t>0507-1428-9618</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 길주로 643 거림타워 13층,14층</t>
+          <t>인천 부평구 부평대로 83 강남타워 9, 10층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miracle.gym02</t>
+          <t>https://blog.naver.com/spoany_70</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w441cj</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1899</v>
+        <v>1528</v>
       </c>
       <c r="Q3" t="n">
-        <v>954</v>
+        <v>2039</v>
       </c>
       <c r="R3" t="n">
-        <v>2853</v>
+        <v>3567</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>35823978</t>
+          <t>1163734622</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35823978</t>
+          <t>https://m.place.naver.com/place/1163734622</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -756,34 +760,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포애니 부평시장역점</t>
+          <t>짐박스피트니스 부평시장역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spoany_70@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1428-9618</t>
+          <t>0507-1471-0163</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평대로 83 강남타워 9, 10층</t>
+          <t>인천 부평구 부흥로 277 1~4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_70</t>
+          <t>https://gymboxx.com/onceinayear?gym=72</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -798,13 +806,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +825,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1527</v>
+        <v>2048</v>
       </c>
       <c r="Q4" t="n">
-        <v>2039</v>
+        <v>74</v>
       </c>
       <c r="R4" t="n">
-        <v>3566</v>
+        <v>2122</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +840,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1163734622</t>
+          <t>1569809175</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163734622</t>
+          <t>https://m.place.naver.com/place/1569809175</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -850,38 +862,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>짐박스피트니스 부평시장역점</t>
+          <t>스포애니 부평역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>spoany86@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1471-0163</t>
+          <t>0507-1339-9618</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부흥로 277 1~4층</t>
+          <t>인천 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=72</t>
+          <t>https://blog.naver.com/spoany86</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -896,13 +904,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4aher</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -911,13 +923,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2048</v>
+        <v>1316</v>
       </c>
       <c r="Q5" t="n">
-        <v>74</v>
+        <v>3066</v>
       </c>
       <c r="R5" t="n">
-        <v>2122</v>
+        <v>4382</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,17 +938,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1569809175</t>
+          <t>1118966019</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1569809175</t>
+          <t>https://m.place.naver.com/place/1118966019</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -948,29 +960,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 부평역점</t>
+          <t>올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany86@naver.com</t>
+          <t>all_night_b@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1339-9618</t>
+          <t>0507-1334-5596</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
+          <t>인천 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany86</t>
+          <t>https://www.instagram.com/all.night_official</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,15 +997,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41wqc</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1005,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="Q6" t="n">
-        <v>3067</v>
+        <v>920</v>
       </c>
       <c r="R6" t="n">
-        <v>4383</v>
+        <v>2233</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,17 +1036,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1118966019</t>
+          <t>1342318850</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1118966019</t>
+          <t>https://m.place.naver.com/place/1342318850</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1042,34 +1058,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 부평점</t>
+          <t>피트니스 연구소 부평산곡점 헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>lfitness5@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1334-5596</t>
+          <t>0507-1349-2251</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
+          <t>인천 부평구 원적로 295 더 루츠 스퀘어 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/all.night_official</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1079,18 +1095,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40cxc</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1099,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1311</v>
+        <v>986</v>
       </c>
       <c r="Q7" t="n">
-        <v>920</v>
+        <v>493</v>
       </c>
       <c r="R7" t="n">
-        <v>2231</v>
+        <v>1479</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,17 +1134,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1342318850</t>
+          <t>1338376061</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342318850</t>
+          <t>https://m.place.naver.com/place/1338376061</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1136,34 +1156,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
+          <t>카우짐 백운역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ironfitnesssamsan@naver.com</t>
+          <t>cowgym_24@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1483-2126</t>
+          <t>0507-1370-4255</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평북로 448 로얄프라자 2층</t>
+          <t>인천 부평구 마장로 75 대경빌딩 B1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ironfitnesssamsan</t>
+          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1178,13 +1198,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w413n5</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1193,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>710</v>
+        <v>801</v>
       </c>
       <c r="Q8" t="n">
-        <v>291</v>
+        <v>433</v>
       </c>
       <c r="R8" t="n">
-        <v>1001</v>
+        <v>1234</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,17 +1232,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1098353648</t>
+          <t>1852598877</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098353648</t>
+          <t>https://m.place.naver.com/place/1852598877</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1230,34 +1254,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피트니스 연구소 부평산곡점 헬스PT</t>
+          <t>무무짐 헬스PT 부평삼산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lfitness5@naver.com</t>
+          <t>moomoogym33@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1349-2251</t>
+          <t>0507-1353-7334</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천 부평구 충선로203번길 24 801호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://www.instagram.com/moomoogym33/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1267,18 +1291,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ioux</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1287,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>986</v>
+        <v>558</v>
       </c>
       <c r="Q9" t="n">
-        <v>493</v>
+        <v>297</v>
       </c>
       <c r="R9" t="n">
-        <v>1479</v>
+        <v>855</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,51 +1330,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1338376061</t>
+          <t>1304139561</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338376061</t>
+          <t>https://m.place.naver.com/place/1304139561</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>필라테스 린 산곡점</t>
+          <t>그루비짐24 헬스PT 부개점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pilateslean_sangok@naver.com</t>
+          <t>da_tos@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1311-1654</t>
+          <t>0507-1443-5643</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 부평구 원적로 412 5층</t>
+          <t>인천 부평구 충선로 174 301, 401호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
+          <t>https://blog.naver.com/da_tos</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1366,10 +1394,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wtvzl30</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,17 +1409,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>199</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>544</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,47 +1428,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2024471908</t>
+          <t>2052607694</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024471908</t>
+          <t>https://m.place.naver.com/place/2052607694</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>온정필라테스&amp;PT 산곡점</t>
+          <t>PT의정석 운동재활센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ktg191800@naver.com</t>
+          <t>standardpt_1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1491-9679</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 부평구 마장로 320 2층 207호, 산곡역 2번출구에서 도보 2분 한화프라자 2층</t>
+          <t>인천 부평구 대정로 24 희경빌딩 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ktg191800</t>
+          <t>https://blog.naver.com/standardpt_1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1461,7 +1497,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4lmji</t>
+          <t>https://talk.naver.com/ct/w4mxjb</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1471,17 +1507,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>328</v>
+        <v>110</v>
       </c>
       <c r="Q11" t="n">
-        <v>609</v>
+        <v>67</v>
       </c>
       <c r="R11" t="n">
-        <v>937</v>
+        <v>177</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,17 +1526,111 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1452652224</t>
+          <t>1311384236</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1452652224</t>
+          <t>https://m.place.naver.com/place/1311384236</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>필라테스 린 산곡점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pilateslean_sangok@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1311-1654</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천 부평구 원적로 412 5층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2024471908</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024471908</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부평_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부평_헬스장.xlsx
@@ -426,7 +426,7 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="Q2" t="n">
         <v>955</v>
       </c>
       <c r="R2" t="n">
-        <v>2854</v>
+        <v>2856</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="Q3" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="R3" t="n">
         <v>3567</v>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2048</v>
+        <v>2045</v>
       </c>
       <c r="Q4" t="n">
         <v>74</v>
       </c>
       <c r="R4" t="n">
-        <v>2122</v>
+        <v>2119</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="Q5" t="n">
         <v>3066</v>
       </c>
       <c r="R5" t="n">
-        <v>4382</v>
+        <v>4383</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -960,29 +960,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 부평점</t>
+          <t>머슬프로짐 PT 헬스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>rkdals5404@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1334-5596</t>
+          <t>0507-1445-7902</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
+          <t>인천 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/all.night_official</t>
+          <t>https://blog.naver.com/rkdals5404</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,19 +997,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41wqc</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1021,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1313</v>
+        <v>1706</v>
       </c>
       <c r="Q6" t="n">
-        <v>920</v>
+        <v>1505</v>
       </c>
       <c r="R6" t="n">
-        <v>2233</v>
+        <v>3211</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1342318850</t>
+          <t>142646646</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342318850</t>
+          <t>https://m.place.naver.com/place/142646646</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1058,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피트니스 연구소 부평산곡점 헬스PT</t>
+          <t>휘트니스피플우먼 부평점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lfitness5@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1349-2251</t>
+          <t>0507-1330-3912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천 부평구 부평대로 19-1 도시프라자빌딩 7층 701호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1105,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40cxc</t>
+          <t>https://talk.naver.com/ct/w44qaq</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1119,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>986</v>
+        <v>1180</v>
       </c>
       <c r="Q7" t="n">
-        <v>493</v>
+        <v>924</v>
       </c>
       <c r="R7" t="n">
-        <v>1479</v>
+        <v>2104</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1338376061</t>
+          <t>1619023009</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338376061</t>
+          <t>https://m.place.naver.com/place/1619023009</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1156,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>카우짐 백운역점</t>
+          <t>피트니스 연구소 부평산곡점 헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cowgym_24@naver.com</t>
+          <t>lfitness5@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1370-4255</t>
+          <t>0507-1349-2251</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 부평구 마장로 75 대경빌딩 B1층</t>
+          <t>인천 부평구 원적로 295 더 루츠 스퀘어 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1203,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w413n5</t>
+          <t>https://talk.naver.com/ct/w40cxc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1217,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>801</v>
+        <v>986</v>
       </c>
       <c r="Q8" t="n">
-        <v>433</v>
+        <v>494</v>
       </c>
       <c r="R8" t="n">
-        <v>1234</v>
+        <v>1480</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1852598877</t>
+          <t>1338376061</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852598877</t>
+          <t>https://m.place.naver.com/place/1338376061</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1254,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>무무짐 헬스PT 부평삼산점</t>
+          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>moomoogym33@naver.com</t>
+          <t>msgym_01@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1353-7334</t>
+          <t>032-330-3334</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 부평구 충선로203번길 24 801호</t>
+          <t>인천 부평구 체육관로 34 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moomoogym33/</t>
+          <t>https://blog.naver.com/msgym_01/223768835115</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1291,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1301,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ioux</t>
+          <t>https://talk.naver.com/ct/wcbsfx</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1315,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>558</v>
+        <v>900</v>
       </c>
       <c r="Q9" t="n">
-        <v>297</v>
+        <v>460</v>
       </c>
       <c r="R9" t="n">
-        <v>855</v>
+        <v>1360</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1304139561</t>
+          <t>1350569862</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1304139561</t>
+          <t>https://m.place.naver.com/place/1350569862</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1352,34 +1348,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>그루비짐24 헬스PT 부개점</t>
+          <t>카우짐 백운역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>da_tos@naver.com</t>
+          <t>cowgym_24@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1443-5643</t>
+          <t>0507-1370-4255</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 부평구 충선로 174 301, 401호</t>
+          <t>인천 부평구 마장로 75 대경빌딩 B1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/da_tos</t>
+          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1399,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wtvzl30</t>
+          <t>https://talk.naver.com/ct/w413n5</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1413,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>345</v>
+        <v>801</v>
       </c>
       <c r="Q10" t="n">
-        <v>199</v>
+        <v>433</v>
       </c>
       <c r="R10" t="n">
-        <v>544</v>
+        <v>1234</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2052607694</t>
+          <t>1852598877</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2052607694</t>
+          <t>https://m.place.naver.com/place/1852598877</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1445,34 +1441,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PT의정석 운동재활센터</t>
+          <t>필라테스 린 산곡점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>standardpt_1@naver.com</t>
+          <t>pilateslean_sangok@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1491-9679</t>
+          <t>0507-1311-1654</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 부평구 대정로 24 희경빌딩 3층</t>
+          <t>인천 부평구 원적로 412 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/standardpt_1</t>
+          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1497,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mxjb</t>
+          <t>https://talk.naver.com/ct/wgildz7</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,17 +1503,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>177</v>
+        <v>3</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1526,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1311384236</t>
+          <t>2024471908</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1311384236</t>
+          <t>https://m.place.naver.com/place/2024471908</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1548,29 +1544,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>필라테스 린 산곡점</t>
+          <t>온정필라테스&amp;PT 산곡점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pilateslean_sangok@naver.com</t>
+          <t>ktg191800@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1311-1654</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천 부평구 원적로 412 5층</t>
+          <t>인천 부평구 마장로 320 2층 207호, 산곡역 2번출구에서 도보 2분 한화프라자 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
+          <t>https://blog.naver.com/ktg191800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1590,10 +1582,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lmji</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1605,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>610</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>938</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,12 +1616,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2024471908</t>
+          <t>1452652224</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024471908</t>
+          <t>https://m.place.naver.com/place/1452652224</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/부평_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부평_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
+          <t>인천광역시 부평구 길주로 643 거림타워 13층,14층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/webpfty</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 부평구 부평대로 83 강남타워 9, 10층</t>
+          <t>인천광역시 부평구 부평대로 83 강남타워 9, 10층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w441cj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -748,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -781,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 부평구 부흥로 277 1~4층</t>
+          <t>인천광역시 부평구 부흥로 277 1~4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -806,14 +798,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4iwq7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -850,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -879,7 +867,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
+          <t>인천광역시 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -904,14 +892,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4aher</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -926,10 +910,10 @@
         <v>1317</v>
       </c>
       <c r="Q5" t="n">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="R5" t="n">
-        <v>4383</v>
+        <v>4382</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -948,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -977,7 +961,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
+          <t>인천광역시 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1042,7 +1026,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1115,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="Q7" t="n">
         <v>924</v>
       </c>
       <c r="R7" t="n">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1124,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1163,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,7 +1173,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1204,7 +1188,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1238,7 +1222,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1336,46 +1320,46 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>카우짐 백운역점</t>
+          <t>3세트짐 체형교정센터 부평본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cowgym_24@naver.com</t>
+          <t>lineup_pt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1370-4255</t>
+          <t>0507-1323-8788</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 부평구 마장로 75 대경빌딩 B1층</t>
+          <t>인천 부평구 경원대로 1404 1003호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/12/bizes/934147/items/5159258?area=pll&amp;theme=place</t>
+          <t>https://blog.naver.com/lineup_pt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1395,7 +1379,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w413n5</t>
+          <t>https://talk.naver.com/ct/w4eq6k9</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1393,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>801</v>
+        <v>369</v>
       </c>
       <c r="Q10" t="n">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="R10" t="n">
-        <v>1234</v>
+        <v>825</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1408,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1852598877</t>
+          <t>1774897291</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852598877</t>
+          <t>https://m.place.naver.com/place/1774897291</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1446,29 +1430,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>필라테스 린 산곡점</t>
+          <t>온정필라테스&amp;PT 산곡점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pilateslean_sangok@naver.com</t>
+          <t>ktg191800@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1311-1654</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 부평구 원적로 412 5층</t>
+          <t>인천 부평구 마장로 320 2층 207호, 산곡역 2번출구에서 도보 2분 한화프라자 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilateslean_sangok/224258799074</t>
+          <t>https://blog.naver.com/ktg191800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1493,7 +1473,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wgildz7</t>
+          <t>https://talk.naver.com/ct/w4lmji</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1487,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>611</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>939</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,111 +1502,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2024471908</t>
+          <t>1452652224</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024471908</t>
+          <t>https://m.place.naver.com/place/1452652224</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>온정필라테스&amp;PT 산곡점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ktg191800@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>인천 부평구 마장로 320 2층 207호, 산곡역 2번출구에서 도보 2분 한화프라자 2층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/ktg191800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4lmji</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>328</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>610</v>
-      </c>
-      <c r="R12" t="n">
-        <v>938</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1452652224</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1452652224</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부평_헬스장.xlsx
+++ b/naver-place-crawler/results_health/부평_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
+          <t>그린짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>miraclebym02@naver.com</t>
+          <t>green_gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1412-0034</t>
+          <t>0507-1482-4423</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 길주로 643 거림타워 13층,14층</t>
+          <t>인천 부평구 부평북로 339 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miracle.gym02</t>
+          <t>https://blog.naver.com/green_gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,18 +601,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fs9p</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1901</v>
+        <v>321</v>
       </c>
       <c r="Q2" t="n">
-        <v>955</v>
+        <v>822</v>
       </c>
       <c r="R2" t="n">
-        <v>2856</v>
+        <v>1143</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>35823978</t>
+          <t>1527477204</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35823978</t>
+          <t>https://m.place.naver.com/place/1527477204</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스포애니 부평시장역점</t>
+          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spoany_70@naver.com</t>
+          <t>miraclebym02@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1428-9618</t>
+          <t>0507-1412-0034</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부평대로 83 강남타워 9, 10층</t>
+          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_70</t>
+          <t>https://www.instagram.com/miracle.gym02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/webpfty</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1529</v>
+        <v>1901</v>
       </c>
       <c r="Q3" t="n">
-        <v>2038</v>
+        <v>955</v>
       </c>
       <c r="R3" t="n">
-        <v>3567</v>
+        <v>2856</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1163734622</t>
+          <t>35823978</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163734622</t>
+          <t>https://m.place.naver.com/place/35823978</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,38 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>짐박스피트니스 부평시장역점</t>
+          <t>스포애니 부평시장역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
+          <t>spoany_70@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1471-0163</t>
+          <t>0507-1428-9618</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부흥로 277 1~4층</t>
+          <t>인천 부평구 부평대로 83 강남타워 9, 10층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://gymboxx.com/onceinayear?gym=72</t>
+          <t>https://blog.naver.com/spoany_70</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -798,13 +802,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w441cj</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2045</v>
+        <v>1529</v>
       </c>
       <c r="Q4" t="n">
-        <v>74</v>
+        <v>2038</v>
       </c>
       <c r="R4" t="n">
-        <v>2119</v>
+        <v>3567</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1569809175</t>
+          <t>1163734622</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1569809175</t>
+          <t>https://m.place.naver.com/place/1163734622</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,34 +858,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 부평역점</t>
+          <t>짐박스피트니스 부평시장역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany86@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>gymboxx@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>info@suppliesfitness.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1339-9618</t>
+          <t>0507-1471-0163</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
+          <t>인천 부평구 부흥로 277 1~4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany86</t>
+          <t>https://gymboxx.com/onceinayear?gym=72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -892,13 +904,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iwq7</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +923,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1317</v>
+        <v>2045</v>
       </c>
       <c r="Q5" t="n">
-        <v>3065</v>
+        <v>76</v>
       </c>
       <c r="R5" t="n">
-        <v>4382</v>
+        <v>2121</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +938,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1118966019</t>
+          <t>1569809175</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1118966019</t>
+          <t>https://m.place.naver.com/place/1569809175</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,29 +960,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>머슬프로짐 PT 헬스</t>
+          <t>스포애니 부평역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rkdals5404@naver.com</t>
+          <t>spoany86@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1445-7902</t>
+          <t>0507-1339-9618</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
+          <t>인천 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rkdals5404</t>
+          <t>https://blog.naver.com/spoany86</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -986,10 +1002,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4aher</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1706</v>
+        <v>1317</v>
       </c>
       <c r="Q6" t="n">
-        <v>1505</v>
+        <v>3065</v>
       </c>
       <c r="R6" t="n">
-        <v>3211</v>
+        <v>4382</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1036,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>142646646</t>
+          <t>1118966019</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/142646646</t>
+          <t>https://m.place.naver.com/place/1118966019</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,29 +1058,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>휘트니스피플우먼 부평점</t>
+          <t>머슬프로짐 PT 헬스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fpeoplew1@naver.com</t>
+          <t>rkdals5404@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1330-3912</t>
+          <t>0507-1445-7902</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 부평구 부평대로 19-1 도시프라자빌딩 7층 701호</t>
+          <t>인천 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fpeoplew1</t>
+          <t>https://blog.naver.com/rkdals5404</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1080,14 +1100,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44qaq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1099,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1181</v>
+        <v>1706</v>
       </c>
       <c r="Q7" t="n">
-        <v>924</v>
+        <v>1505</v>
       </c>
       <c r="R7" t="n">
-        <v>2105</v>
+        <v>3211</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1619023009</t>
+          <t>142646646</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619023009</t>
+          <t>https://m.place.naver.com/place/142646646</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1136,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피트니스 연구소 부평산곡점 헬스PT</t>
+          <t>휘트니스피플우먼 부평점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lfitness5@naver.com</t>
+          <t>fpeoplew1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1349-2251</t>
+          <t>0507-1330-3912</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천 부평구 부평대로 19-1 도시프라자빌딩 7층 701호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://blog.naver.com/fpeoplew1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1173,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1183,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40cxc</t>
+          <t>https://talk.naver.com/ct/w44qaq</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1197,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>986</v>
+        <v>1181</v>
       </c>
       <c r="Q8" t="n">
-        <v>494</v>
+        <v>925</v>
       </c>
       <c r="R8" t="n">
-        <v>1480</v>
+        <v>2106</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1338376061</t>
+          <t>1619023009</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338376061</t>
+          <t>https://m.place.naver.com/place/1619023009</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1234,34 +1250,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엠에스짐 헬스장 헬스 PT 삼산점</t>
+          <t>피트니스 연구소 부평산곡점 헬스PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>msgym_01@naver.com</t>
+          <t>lfitness5@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-330-3334</t>
+          <t>0507-1349-2251</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 부평구 체육관로 34 7층</t>
+          <t>인천 부평구 원적로 295 더 루츠 스퀘어 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/msgym_01/223768835115</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1281,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcbsfx</t>
+          <t>https://talk.naver.com/ct/w40cxc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1295,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>900</v>
+        <v>986</v>
       </c>
       <c r="Q9" t="n">
-        <v>460</v>
+        <v>494</v>
       </c>
       <c r="R9" t="n">
-        <v>1360</v>
+        <v>1480</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1350569862</t>
+          <t>1338376061</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350569862</t>
+          <t>https://m.place.naver.com/place/1338376061</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
